--- a/stories/arbres/ATOM-SEC.ADU.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maya est au magasin. C'est la sortie de l'école. La maîtresse attend près des caisses. Maman est au rayon des pommes. Papa doit les rejoindre. Maya a regardé les crayons. Elle lève les yeux. Elle cherche. Maya se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Maya marche vers les pommes. Elle voit maman. Maman a le panier. Maya va vers maman. Parce qu'elle a cherché maman, elle la trouve. Maman dit : me voici. Tu vas vers papa, maman, ou la maîtresse. Maya prend le manteau de maman. Elle est calme.</t>
+          <t>Maya est au magasin. C'est la sortie de l'école. La maîtresse attend près des caisses. Maman est au rayon des pommes. Papa doit les rejoindre. Maya a regardé les crayons. Elle lève les yeux. Elle cherche. Maya se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Maya marche vers les pommes. Elle voit maman. Maman a le panier. Maya va vers maman. Parce qu'elle a cherché maman, elle la trouve. Me voici. Tu vas vers papa, maman, ou la maîtresse. Maya prend le manteau de maman. Elle est calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maya est au magasin. C'est la sortie de l'école. La maîtresse attend près des caisses. Maman est au rayon des pommes. Papa doit les rejoindre. Maya a regardé les crayons. Elle lève les yeux. Elle cherche. Maya se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Maya marche vers les pommes. Elle voit maman. Maman a le panier. Maya va vers maman. Parce qu'elle a cherché maman, elle la trouve.
+maman|Me voici. Tu vas vers papa, maman, ou la maîtresse.
+narrateur|Maya prend le manteau de maman. Elle est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Maya cherche quelqu'un. Vers qui va-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a cherché maman. Papa et la maîtresse sont aussi des adultes connus.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1840,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maya tient le manteau de maman. Elles paient les pommes.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2007,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2047,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Maya prend le manteau de maman. Elle est calme.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Maya cherche quelqu'un. Vers qui va-t-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1685,7 @@
           <t>narrateur|Maya a cherché maman. Papa et la maîtresse sont aussi des adultes connus.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1845,6 +1857,7 @@
           <t>narrateur|Maya tient le manteau de maman. Elles paient les pommes.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2012,6 +2025,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2068,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2283,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.ADU.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maya retrouve maman au magasin</t>
+          <t>Les pommes et le manteau de maman</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les pommes sentent le jardin. Sarah lève les yeux au magasin. Elle va vers maman. Papa et la maîtresse sont aussi des adultes connus.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maya est au magasin. C'est la sortie de l'école. La maîtresse attend près des caisses. Maman est au rayon des pommes. Papa doit les rejoindre. Maya a regardé les crayons. Elle lève les yeux. Elle cherche. Maya se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Maya marche vers les pommes. Elle voit maman. Maman a le panier. Maya va vers maman. Parce qu'elle a cherché maman, elle la trouve. Me voici. Tu vas vers papa, maman, ou la maîtresse. Maya prend le manteau de maman. Elle est calme.</t>
+          <t>Les pommes sentent le jardin, même ici. Le caddie fait un petit couic. Le sol du magasin est froid et lisse. Un sac d'école pèse encore sur l'épaule. Dehors, le jour baisse un peu. Sarah vit avec papa et maman. C'est la sortie de l'école. En ce moment, Sarah est au magasin. La maîtresse attend près des caisses. Maman est au rayon des pommes. Papa doit les rejoindre. Sarah a regardé les crayons. Les crayons sont dans une boîte claire. Ils brillent, les crayons. Sarah lève les yeux. Elle cherche. Maman ? Sarah se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers les pommes. Sarah marche vers les pommes. Ses pieds restent près du caddie. Le sol est froid sous les chaussures. Elle voit maman. Maman a le panier. Une pomme rouge dépasse. Me voici, Sarah. Je t'ai cherchée. Tu vas vers papa, maman, ou la maîtresse. Bravo. Tu es venue vers maman. La maîtresse est aux caisses. Oui. Papa arrive aussi. Sarah va vers maman. Parce qu'elle a cherché maman, elle la trouve. Sarah prend le manteau de maman. Le manteau est laineux, un peu chaud. Il sent la maison. Tu as fait du bon travail. On reste ensemble. Sarah est calme. Le caddie fait encore couic. Les pommes sentent toujours le jardin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,53 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Maya est au magasin. C'est la sortie de l'école. La maîtresse attend près des caisses. Maman est au rayon des pommes. Papa doit les rejoindre. Maya a regardé les crayons. Elle lève les yeux. Elle cherche. Maya se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Maya marche vers les pommes. Elle voit maman. Maman a le panier. Maya va vers maman. Parce qu'elle a cherché maman, elle la trouve.
-maman|Me voici. Tu vas vers papa, maman, ou la maîtresse.
-narrateur|Maya prend le manteau de maman. Elle est calme.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>enfants_parc</t>
-        </is>
-      </c>
+          <t>narrateur|Les pommes sentent le jardin, même ici.
+narrateur|Le caddie fait un petit couic.
+narrateur|Le sol du magasin est froid et lisse.
+narrateur|Un sac d'école pèse encore sur l'épaule.
+narrateur|Dehors, le jour baisse un peu.
+narrateur|Sarah vit avec papa et maman.
+narrateur|C'est la sortie de l'école.
+narrateur|En ce moment, Sarah est au magasin.
+narrateur|La maîtresse attend près des caisses.
+narrateur|Maman est au rayon des pommes.
+narrateur|Papa doit les rejoindre.
+narrateur|Sarah a regardé les crayons.
+narrateur|Les crayons sont dans une boîte claire.
+enfant-f|Ils brillent, les crayons.
+narrateur|Sarah lève les yeux.
+narrateur|Elle cherche.
+enfant-f|Maman ?
+narrateur|Sarah se souvient.
+narrateur|On va vers papa.
+narrateur|On va vers maman.
+narrateur|On va vers la maîtresse.
+enfant-f|Je vais vers les pommes.
+narrateur|Sarah marche vers les pommes.
+narrateur|Ses pieds restent près du caddie.
+narrateur|Le sol est froid sous les chaussures.
+narrateur|Elle voit maman.
+narrateur|Maman a le panier.
+narrateur|Une pomme rouge dépasse.
+maman|Me voici, Sarah.
+enfant-f|Je t'ai cherchée.
+maman|Tu vas vers papa, maman, ou la maîtresse.
+maman|Bravo. Tu es venue vers maman.
+enfant-f|La maîtresse est aux caisses.
+maman|Oui. Papa arrive aussi.
+narrateur|Sarah va vers maman.
+narrateur|Parce qu'elle a cherché maman, elle la trouve.
+narrateur|Sarah prend le manteau de maman.
+narrateur|Le manteau est laineux, un peu chaud.
+enfant-f|Il sent la maison.
+maman|Tu as fait du bon travail.
+maman|On reste ensemble.
+narrateur|Sarah est calme.
+narrateur|Le caddie fait encore couic.
+narrateur|Les pommes sentent toujours le jardin.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1395,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Maya cherche quelqu'un. Vers qui va-t-elle ?</t>
+          <t>Sarah cherche quelqu'un. Vers qui va-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1555,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Maya cherche quelqu'un. Vers qui va-t-elle ?</t>
+          <t>narrateur|Sarah cherche quelqu'un.
+narrateur|Vers qui va-t-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1584,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maya a cherché maman. Papa et la maîtresse sont aussi des adultes connus.</t>
+          <t>Sarah a cherché maman. Elle est allée vers maman. Tu es venue vers moi ? Oui. Vers maman. Bravo, Sarah. Papa et la maîtresse sont aussi des adultes connus. Sarah tient encore le manteau.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1682,7 +1732,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maya a cherché maman. Papa et la maîtresse sont aussi des adultes connus.</t>
+          <t>narrateur|Sarah a cherché maman.
+narrateur|Elle est allée vers maman.
+maman|Tu es venue vers moi ?
+enfant-f|Oui. Vers maman.
+maman|Bravo, Sarah.
+maman|Papa et la maîtresse sont aussi des adultes connus.
+narrateur|Sarah tient encore le manteau.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1710,7 +1766,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maya tient le manteau de maman. Elles paient les pommes.</t>
+          <t>Papa arrive près des pommes. Me voici. Tu es avec maman ? Oui, papa. Bravo. Tu vas vers papa, maman, ou la maîtresse. Ils vont vers les caisses. La maîtresse fait un petit signe. Sarah tient le manteau de maman. Elles paient les pommes. Tu as fini, Sarah ? Oui. Les pommes sont à nous.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1854,7 +1910,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maya tient le manteau de maman. Elles paient les pommes.</t>
+          <t>narrateur|Papa arrive près des pommes.
+papa|Me voici.
+papa|Tu es avec maman ?
+enfant-f|Oui, papa.
+papa|Bravo. Tu vas vers papa, maman, ou la maîtresse.
+narrateur|Ils vont vers les caisses.
+narrateur|La maîtresse fait un petit signe.
+narrateur|Sarah tient le manteau de maman.
+narrateur|Elles paient les pommes.
+maman|Tu as fini, Sarah ?
+enfant-f|Oui. Les pommes sont à nous.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1882,7 +1948,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je suis allée vers maman. Bravo. Tu as fait du bon travail. Le sac sent les pommes. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2022,7 +2088,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Je suis allée vers maman.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le sac sent les pommes.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2044,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2082,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les pommes sentent le jardin, même ici. Le caddie fait un petit couic. Le sol du magasin est froid et lisse. Un sac d'école pèse encore sur l'épaule. Dehors, le jour baisse un peu. Sarah vit avec papa et maman. C'est la sortie de l'école. En ce moment, Sarah est au magasin. La maîtresse attend près des caisses. Maman est au rayon des pommes. Papa doit les rejoindre. Sarah a regardé les crayons. Les crayons sont dans une boîte claire. Ils brillent, les crayons. Sarah lève les yeux. Elle cherche. Maman ? Sarah se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers les pommes. Sarah marche vers les pommes. Ses pieds restent près du caddie. Le sol est froid sous les chaussures. Elle voit maman. Maman a le panier. Une pomme rouge dépasse. Me voici, Sarah. Je t'ai cherchée. Tu vas vers papa, maman, ou la maîtresse. Bravo. Tu es venue vers maman. La maîtresse est aux caisses. Oui. Papa arrive aussi. Sarah va vers maman. Parce qu'elle a cherché maman, elle la trouve. Sarah prend le manteau de maman. Le manteau est laineux, un peu chaud. Il sent la maison. Tu as fait du bon travail. On reste ensemble. Sarah est calme. Le caddie fait encore couic. Les pommes sentent toujours le jardin.</t>
+          <t>Les pommes sentent le jardin, même ici. Une pomme verte a une petite feuille. Le caddie fait un petit couic. Une roue tourne, puis s'arrête. Le sol du magasin est froid et lisse. Un sac d'école pèse encore sur l'épaule. La sangle laisse une marque tiède. Dehors, le jour baisse un peu. Sarah vit avec papa et maman. C'est la sortie de l'école. En ce moment, Sarah est au magasin. La maîtresse attend près des caisses. Maman est au rayon des pommes. Papa doit les rejoindre. Sarah a regardé les crayons. Les crayons sont dans une boîte claire. Ils brillent, les crayons. Sarah lève les yeux. Elle cherche. Maman ? Sarah se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers les pommes. Sarah marche vers les pommes. Ses pieds restent près du caddie. Le sol est froid sous les chaussures. Elle passe devant les caisses. La maîtresse est là, tout près. Sarah continue vers les pommes. Elle voit maman. Maman a le panier. Une pomme rouge dépasse. Me voici, Sarah. Je t'ai cherchée. Tu vas vers papa, maman, ou la maîtresse. Bravo. Tu es venue vers maman. La maîtresse est aux caisses. Oui. Papa arrive aussi. Sarah va vers maman. Parce qu'elle a cherché maman, elle la trouve. Sarah prend le manteau de maman. Le manteau est laineux, un peu chaud. Il sent la maison. On reste ensemble. Sarah est calme. Le caddie fait encore couic. Les pommes sentent toujours le jardin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maya est au magasin. C'est la sortie de l'école. La maîtresse attend près des caisses. Maman est au rayon des pommes. &lt;emphasis level="moderate"&gt;papa&lt;/emphasis&gt; doit les rejoindre. Maya a regardé les crayons. Elle lève les yeux. Elle cherche. Maya se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Maya marche vers les pommes. Elle voit maman. Maman a le panier. Maya va vers maman. Parce qu'elle a cherché maman, elle la trouve. Maman dit : me voici. Tu vas vers papa, maman, ou la maîtresse. Maya prend le manteau de maman. Elle est calme.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les pommes sentent le jardin, même ici. Une pomme verte a une petite feuille. Le caddie fait un petit couic. Une roue tourne, puis s'arrête. Le sol du magasin est froid et lisse. Un sac d'école pèse encore sur l'épaule. La sangle laisse une marque tiède. Dehors, le jour baisse un peu. Sarah vit avec papa et maman. C'est la sortie de l'école. En ce moment, Sarah est au magasin. La maîtresse attend près des caisses. Maman est au rayon des pommes. Papa doit les rejoindre. Sarah a regardé les crayons. Les crayons sont dans une boîte claire. Ils brillent, les crayons. Sarah lève les yeux. Elle cherche. Maman ? Sarah se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers les pommes. Sarah marche vers les pommes. Ses pieds restent près du caddie. Le sol est froid sous les chaussures. Elle passe devant les caisses. La maîtresse est là, tout près. Sarah continue vers les pommes. Elle voit maman. Maman a le panier. Une pomme rouge dépasse. Me voici, Sarah. Je t'ai cherchée. Tu vas vers papa, maman, ou la maîtresse. Bravo. Tu es venue vers maman. La maîtresse est aux caisses. Oui. Papa arrive aussi. Sarah va vers maman. Parce qu'elle a cherché maman, elle la trouve. Sarah prend le manteau de maman. Le manteau est laineux, un peu chaud. Il sent la maison. On reste ensemble. Sarah est calme. Le caddie fait encore couic. Les pommes sentent toujours le jardin.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1325,9 +1325,12 @@
       <c r="AW2" t="inlineStr">
         <is>
           <t>narrateur|Les pommes sentent le jardin, même ici.
+narrateur|Une pomme verte a une petite feuille.
 narrateur|Le caddie fait un petit couic.
+narrateur|Une roue tourne, puis s'arrête.
 narrateur|Le sol du magasin est froid et lisse.
 narrateur|Un sac d'école pèse encore sur l'épaule.
+narrateur|La sangle laisse une marque tiède.
 narrateur|Dehors, le jour baisse un peu.
 narrateur|Sarah vit avec papa et maman.
 narrateur|C'est la sortie de l'école.
@@ -1349,6 +1352,9 @@
 narrateur|Sarah marche vers les pommes.
 narrateur|Ses pieds restent près du caddie.
 narrateur|Le sol est froid sous les chaussures.
+narrateur|Elle passe devant les caisses.
+narrateur|La maîtresse est là, tout près.
+narrateur|Sarah continue vers les pommes.
 narrateur|Elle voit maman.
 narrateur|Maman a le panier.
 narrateur|Une pomme rouge dépasse.
@@ -1363,14 +1369,12 @@
 narrateur|Sarah prend le manteau de maman.
 narrateur|Le manteau est laineux, un peu chaud.
 enfant-f|Il sent la maison.
-maman|Tu as fait du bon travail.
 maman|On reste ensemble.
 narrateur|Sarah est calme.
 narrateur|Le caddie fait encore couic.
 narrateur|Les pommes sentent toujours le jardin.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1400,7 +1404,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Maya cherche quelqu'un. Vers qui va-t-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah cherche quelqu'un. Vers qui va-t-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1559,7 +1563,6 @@
 narrateur|Vers qui va-t-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1589,7 +1592,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Maya a cherché maman. &lt;emphasis level="moderate"&gt;papa&lt;/emphasis&gt; et la maîtresse sont aussi des adultes connus.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a cherché maman. Elle est allée vers maman. Tu es venue vers moi ? Oui. Vers maman. Bravo, Sarah. Papa et la maîtresse sont aussi des adultes connus. Sarah tient encore le manteau.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1741,7 +1744,6 @@
 narrateur|Sarah tient encore le manteau.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1771,7 +1773,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Maya tient le manteau de &lt;emphasis level="moderate"&gt;maman&lt;/emphasis&gt;. Elles paient les pommes.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa arrive près des pommes. Me voici. Tu es avec maman ? Oui, papa. Bravo. Tu vas vers papa, maman, ou la maîtresse. Ils vont vers les caisses. La maîtresse fait un petit signe. Sarah tient le manteau de maman. Elles paient les pommes. Tu as fini, Sarah ? Oui. Les pommes sont à nous.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1914,7 +1916,8 @@
 papa|Me voici.
 papa|Tu es avec maman ?
 enfant-f|Oui, papa.
-papa|Bravo. Tu vas vers papa, maman, ou la maîtresse.
+papa|Bravo.
+papa|Tu vas vers papa, maman, ou la maîtresse.
 narrateur|Ils vont vers les caisses.
 narrateur|La maîtresse fait un petit signe.
 narrateur|Sarah tient le manteau de maman.
@@ -1923,7 +1926,6 @@
 enfant-f|Oui. Les pommes sont à nous.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1948,12 +1950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je suis allée vers maman. Bravo. Tu as fait du bon travail. Le sac sent les pommes. L'histoire est finie.</t>
+          <t>Je suis allée vers maman. Bravo. Le sac sent les pommes.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je suis allée vers maman. Bravo. Le sac sent les pommes.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2090,12 +2092,9 @@
         <is>
           <t>enfant-f|Je suis allée vers maman.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le sac sent les pommes.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le sac sent les pommes.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2114,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2159,6 +2158,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maya, maman, papa, la maîtresse</t>
+          <t>Sarah, maman, papa, la maîtresse</t>
         </is>
       </c>
     </row>
